--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -6616,12 +6616,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -6646,22 +6646,22 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.616468725745654</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_806_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_MRSA</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -6695,7 +6695,7 @@
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_806_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_MRSA</t>
         </is>
       </c>
       <c r="AT32" t="n">
@@ -6708,42 +6708,42 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -6775,12 +6775,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -6805,38 +6805,38 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>387</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_806_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_MRSA</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_806_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_MRSA</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>MRSA</t>
+          <t>Meticillinresistenta gula stafylokocker</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr">
@@ -6896,17 +6896,17 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS MRSA surveillance category.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Source surveillance may include infection or colonization and is not restricted to community-associated MRSA.</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_806_MONTHLY</t>
+          <t>SER_SE_FOHM_SMINET_MRSA</t>
         </is>
       </c>
       <c r="AT33" t="n">
@@ -6942,40 +6942,433 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA33" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB33" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC33" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>methicillin-resistant-staphylococcus-aureus-(mrsa)-surveillance</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP34" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ34" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS34" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV34" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW33" t="inlineStr">
+      <c r="AW34" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
+      <c r="AX34" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY33" t="inlineStr">
+      <c r="AY34" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
+      <c r="AZ34" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA33" t="inlineStr">
+      <c r="BA34" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB33" t="inlineStr">
+      <c r="BB34" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC33" t="inlineStr">
+      <c r="BC34" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>methicillin-resistant-staphylococcus-aureus-(mrsa)-surveillance</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>MRSA</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS MRSA surveillance category.</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN35" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP35" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS35" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV35" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA35" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB35" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -7097,7 +7490,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -7107,7 +7500,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11">
@@ -7127,7 +7520,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -7159,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4436</v>
+        <v>4823</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -5476,13 +5476,13 @@
         </is>
       </c>
       <c r="N26" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O26" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="R26" t="n">
-        <v>4.440129322746721</v>
+        <v>4.457819081004676</v>
       </c>
       <c r="S26" t="inlineStr">
         <is>
@@ -5635,10 +5635,10 @@
         </is>
       </c>
       <c r="N27" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="O27" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="U27" t="inlineStr">
         <is>
@@ -6262,13 +6262,13 @@
         </is>
       </c>
       <c r="N30" t="n">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="O30" t="n">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="R30" t="n">
-        <v>5.094650378291058</v>
+        <v>5.69610215906153</v>
       </c>
       <c r="S30" t="inlineStr">
         <is>
@@ -6421,10 +6421,10 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="O31" t="n">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="U31" t="inlineStr">
         <is>
@@ -6655,13 +6655,13 @@
         </is>
       </c>
       <c r="N32" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="O32" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="R32" t="n">
-        <v>3.616468725745654</v>
+        <v>3.597778964889088</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -6814,10 +6814,10 @@
         </is>
       </c>
       <c r="N33" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="O33" t="n">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="U33" t="inlineStr">
         <is>
@@ -7048,13 +7048,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>0.9552469459295734</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4823</v>
+        <v>4910</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -7048,13 +7048,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="O34" t="n">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="R34" t="n">
-        <v>0.9552469459295734</v>
+        <v>2.211219782244383</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="O35" t="n">
-        <v>54</v>
+        <v>125</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4910</v>
+        <v>4981</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -7048,13 +7048,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="O34" t="n">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="R34" t="n">
-        <v>2.211219782244383</v>
+        <v>3.591020926364878</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="O35" t="n">
-        <v>125</v>
+        <v>203</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4981</v>
+        <v>5059</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7048,13 +7048,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>203</v>
+        <v>276</v>
       </c>
       <c r="O34" t="n">
-        <v>203</v>
+        <v>276</v>
       </c>
       <c r="R34" t="n">
-        <v>3.591020926364878</v>
+        <v>4.882373279195597</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>203</v>
+        <v>276</v>
       </c>
       <c r="O35" t="n">
-        <v>203</v>
+        <v>276</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7552,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5059</v>
+        <v>5132</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN7" t="b">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4155,7 +4155,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5727,7 +5727,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN27" t="b">
@@ -6513,7 +6513,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -7048,13 +7048,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="O34" t="n">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="R34" t="n">
-        <v>4.882373279195597</v>
+        <v>5.855309983383126</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="O35" t="n">
-        <v>276</v>
+        <v>331</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -7369,6 +7369,792 @@
         </is>
       </c>
       <c r="BC35" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>methicillin-resistant-staphylococcus-aureus-(mrsa)-surveillance</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>387</v>
+      </c>
+      <c r="O36" t="n">
+        <v>387</v>
+      </c>
+      <c r="R36" t="n">
+        <v>3.616468725745654</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MRSA</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MRSA</t>
+        </is>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>methicillin-resistant-staphylococcus-aureus-(mrsa)-surveillance</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>387</v>
+      </c>
+      <c r="O37" t="n">
+        <v>387</v>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MRSA</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MRSA</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Meticillinresistenta gula stafylokocker</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; Source surveillance may include infection or colonization and is not restricted to community-associated MRSA.</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_MRSA</t>
+        </is>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>methicillin-resistant-staphylococcus-aureus-(mrsa)-surveillance</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>27</v>
+      </c>
+      <c r="O38" t="n">
+        <v>27</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.4776234729647867</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ38" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>methicillin-resistant-staphylococcus-aureus-(mrsa)-surveillance</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>27</v>
+      </c>
+      <c r="O39" t="n">
+        <v>27</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>MRSA</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS MRSA surveillance category.</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN39" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_806_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -7407,7 +8193,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -7490,7 +8276,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10">
@@ -7500,7 +8286,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -7520,7 +8306,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -7552,7 +8338,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5132</v>
+        <v>5601</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -7048,13 +7048,13 @@
         </is>
       </c>
       <c r="N34" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O34" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="R34" t="n">
-        <v>5.855309983383126</v>
+        <v>5.890689499899036</v>
       </c>
       <c r="S34" t="inlineStr">
         <is>
@@ -7207,10 +7207,10 @@
         </is>
       </c>
       <c r="N35" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="O35" t="n">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="U35" t="inlineStr">
         <is>
@@ -7834,13 +7834,13 @@
         </is>
       </c>
       <c r="N38" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="O38" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="R38" t="n">
-        <v>0.4776234729647867</v>
+        <v>1.309042111088675</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -7993,10 +7993,10 @@
         </is>
       </c>
       <c r="N39" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="O39" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="U39" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5601</v>
+        <v>5650</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O16" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="R16" t="n">
-        <v>3.065120780476937</v>
+        <v>3.055775900048654</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -3670,10 +3670,10 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="O17" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="U17" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5650</v>
+        <v>5649</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -80074,13 +80074,13 @@
         </is>
       </c>
       <c r="N564" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O564" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R564" t="n">
-        <v>0.0179330899199321</v>
+        <v>0.01912862924792757</v>
       </c>
       <c r="U564" t="inlineStr">
         <is>
@@ -89794,7 +89794,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9970</v>
+        <v>9971</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -69196,13 +69196,13 @@
         </is>
       </c>
       <c r="N487" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O487" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R487" t="n">
-        <v>0.02869294387189136</v>
+        <v>0.02988848319988684</v>
       </c>
       <c r="U487" t="inlineStr">
         <is>
@@ -76825,13 +76825,13 @@
         </is>
       </c>
       <c r="N541" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="O541" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="R541" t="n">
-        <v>5.890689499899036</v>
+        <v>5.908379258156991</v>
       </c>
       <c r="U541" t="inlineStr">
         <is>
@@ -87277,13 +87277,13 @@
         </is>
       </c>
       <c r="N615" t="n">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="O615" t="n">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="R615" t="n">
-        <v>1.309042111088675</v>
+        <v>2.600394463919394</v>
       </c>
       <c r="U615" t="inlineStr">
         <is>
@@ -88693,13 +88693,13 @@
         </is>
       </c>
       <c r="N625" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O625" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R625" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.02151970790391852</v>
       </c>
       <c r="U625" t="inlineStr">
         <is>
@@ -89794,7 +89794,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9971</v>
+        <v>10047</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -80074,13 +80074,13 @@
         </is>
       </c>
       <c r="N564" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O564" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="R564" t="n">
-        <v>0.01912862924792757</v>
+        <v>0.02032416857592305</v>
       </c>
       <c r="U564" t="inlineStr">
         <is>
@@ -88693,13 +88693,13 @@
         </is>
       </c>
       <c r="N625" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O625" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R625" t="n">
-        <v>0.02151970790391852</v>
+        <v>0.022715247231914</v>
       </c>
       <c r="U625" t="inlineStr">
         <is>
@@ -89794,7 +89794,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10047</v>
+        <v>10049</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -80074,13 +80074,13 @@
         </is>
       </c>
       <c r="N564" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O564" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R564" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.02151970790391852</v>
       </c>
       <c r="U564" t="inlineStr">
         <is>
@@ -89794,7 +89794,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10049</v>
+        <v>10050</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -87421,13 +87421,13 @@
         </is>
       </c>
       <c r="N616" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O616" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="R616" t="n">
-        <v>0.02032416857592305</v>
+        <v>0.02151970790391852</v>
       </c>
       <c r="U616" t="inlineStr">
         <is>
@@ -89613,6 +89613,150 @@
       <c r="BC631" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>methicillin-resistant-staphylococcus-aureus-(mrsa)-surveillance</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>D236</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>Methicillin-resistant Staphylococcus aureus (MRSA) surveillance</t>
+        </is>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>耐甲氧西林金黄色葡萄球菌（MRSA）监测</t>
+        </is>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N632" t="n">
+        <v>22</v>
+      </c>
+      <c r="O632" t="n">
+        <v>22</v>
+      </c>
+      <c r="R632" t="n">
+        <v>0.02630186521590041</v>
+      </c>
+      <c r="U632" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AA632" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AO632" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP632" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS632" t="inlineStr">
+        <is>
+          <t>HOLD_DE_6ea32e254214cab9f62091fadbc0</t>
+        </is>
+      </c>
+      <c r="AT632" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV632" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="AW632" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="AX632" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="AY632" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
+        </is>
+      </c>
+      <c r="AZ632" t="inlineStr">
+        <is>
+          <t>rki_survstat</t>
+        </is>
+      </c>
+      <c r="BA632" t="inlineStr">
+        <is>
+          <t>Germany RKI SurvStat 2.0</t>
+        </is>
+      </c>
+      <c r="BB632" t="inlineStr">
+        <is>
+          <t>https://survstat.rki.de/Content/Query/Create.aspx</t>
+        </is>
+      </c>
+      <c r="BC632" t="inlineStr">
+        <is>
+          <t>official_webforms_csv_export</t>
         </is>
       </c>
     </row>
@@ -89649,7 +89793,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
     </row>
@@ -89732,7 +89876,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="10">
@@ -89742,7 +89886,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="11">
@@ -89794,7 +89938,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10050</v>
+        <v>10073</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d236/2026-2029.xlsx
+++ b/diseases/d236/2026-2029.xlsx
@@ -89683,13 +89683,13 @@
         </is>
       </c>
       <c r="N632" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O632" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="R632" t="n">
-        <v>0.02630186521590041</v>
+        <v>0.02988848319988684</v>
       </c>
       <c r="U632" t="inlineStr">
         <is>
@@ -89938,7 +89938,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>10073</v>
+        <v>10076</v>
       </c>
     </row>
     <row r="16">
